--- a/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
+++ b/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDAC04D-F7DC-4791-8F77-E51233B3FE91}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DC0D05-D2A6-4E58-B2A6-D5AAFAE59143}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7CA062FE-945D-4C76-A68F-9B28474BFFEC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="235">
   <si>
     <t>UNIDAD</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>RECOMENDACIONES</t>
-  </si>
-  <si>
-    <t>Gerencia de Planeación y Gestión Constitucional</t>
   </si>
   <si>
     <t xml:space="preserve">Direccionamiento Estratégico </t>
@@ -1141,6 +1138,9 @@
       </rPr>
       <t>Formalizar, junto con la OM-03 de este informe, un mecanismo estandarizado y con plazo definido para la apertura, seguimiento y cierre de oportunidades de mejora derivadas de incumplimientos de indicadores, y dejar evidencia trazable de su gestión en Kawak o en el nuevo sistema integral de indicadores. Por otro lado generar los seguimientos correspondientes que garanticen la oportunidad en la alimentación de los indicadores en los tiempos establecidos por los líderes de los procesos.</t>
     </r>
+  </si>
+  <si>
+    <t>Gerencia de Planeación y Gestión Institucional</t>
   </si>
 </sst>
 </file>
@@ -1669,1927 +1669,1927 @@
     </row>
     <row r="2" spans="1:7" s="13" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="6" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="15"/>
+    </row>
+    <row r="12" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="G24" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="17" t="s">
         <v>74</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>75</v>
       </c>
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="17" t="s">
         <v>80</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>81</v>
       </c>
       <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="G29" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G29" s="6" t="s">
+    </row>
+    <row r="30" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="G30" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="G31" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="6" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="G32" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="G33" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="G34" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="6" t="s">
+    </row>
+    <row r="35" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="8" t="s">
+      <c r="F35" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="G35" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="G36" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="G37" s="18" t="s">
         <v>107</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>109</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>110</v>
       </c>
       <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="8" t="s">
+      <c r="F39" s="17" t="s">
         <v>112</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>113</v>
       </c>
       <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G40" s="18"/>
-    </row>
-    <row r="41" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="8" t="s">
+      <c r="F41" s="17" t="s">
         <v>116</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>117</v>
       </c>
       <c r="G41" s="18"/>
     </row>
     <row r="42" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F42" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G42" s="18"/>
-    </row>
-    <row r="43" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="8" t="s">
+      <c r="F43" s="17" t="s">
         <v>120</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>121</v>
       </c>
       <c r="G43" s="18"/>
     </row>
     <row r="44" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="G44" s="18" t="s">
         <v>123</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="G45" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="G46" s="18" t="s">
         <v>129</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="G47" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G47" s="18" t="s">
+    </row>
+    <row r="48" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="8" t="s">
+      <c r="F48" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="G48" s="18" t="s">
         <v>135</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E49" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F49" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="G49" s="18" t="s">
         <v>138</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C50" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="8" t="s">
+      <c r="F50" s="17" t="s">
         <v>141</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>142</v>
       </c>
       <c r="G50" s="18"/>
     </row>
     <row r="51" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F51" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>144</v>
       </c>
       <c r="G51" s="18"/>
     </row>
     <row r="52" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F52" s="17" t="s">
         <v>145</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>146</v>
       </c>
       <c r="G52" s="18"/>
     </row>
     <row r="53" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E53" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="17" t="s">
         <v>147</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>148</v>
       </c>
       <c r="G53" s="18"/>
     </row>
     <row r="54" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F54" s="17" t="s">
         <v>149</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>150</v>
       </c>
       <c r="G54" s="18"/>
     </row>
     <row r="55" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E55" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="G55" s="18" t="s">
         <v>152</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E56" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="G56" s="18" t="s">
         <v>155</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E57" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F57" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="G57" s="18" t="s">
         <v>158</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="G58" s="18" t="s">
         <v>161</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F59" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="G59" s="18" t="s">
         <v>164</v>
-      </c>
-      <c r="G59" s="18" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E60" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F60" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="G60" s="18" t="s">
         <v>167</v>
-      </c>
-      <c r="G60" s="18" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E61" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F61" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="G61" s="19" t="s">
         <v>170</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="8" t="s">
+      <c r="F62" s="17" t="s">
         <v>173</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>174</v>
       </c>
       <c r="G62" s="19"/>
     </row>
     <row r="63" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E63" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F63" s="17" t="s">
         <v>175</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>176</v>
       </c>
       <c r="G63" s="19"/>
     </row>
     <row r="64" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E64" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F64" s="17" t="s">
         <v>177</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>178</v>
       </c>
       <c r="G64" s="19"/>
     </row>
     <row r="65" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E65" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F65" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="G65" s="19"/>
+    </row>
+    <row r="66" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G65" s="19"/>
-    </row>
-    <row r="66" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="8" t="s">
+      <c r="F66" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="G66" s="19"/>
+    </row>
+    <row r="67" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G66" s="19"/>
-    </row>
-    <row r="67" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="8" t="s">
+      <c r="F67" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="G67" s="19"/>
+    </row>
+    <row r="68" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="G67" s="19"/>
-    </row>
-    <row r="68" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="8" t="s">
+      <c r="F68" s="17" t="s">
         <v>185</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>186</v>
       </c>
       <c r="G68" s="19"/>
     </row>
     <row r="69" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E69" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="G69" s="19"/>
+    </row>
+    <row r="70" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="G69" s="19"/>
-    </row>
-    <row r="70" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="F70" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="G70" s="19"/>
+    </row>
+    <row r="71" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="G70" s="19"/>
-    </row>
-    <row r="71" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="8" t="s">
+      <c r="F71" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="G71" s="19"/>
+    </row>
+    <row r="72" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G71" s="19"/>
-    </row>
-    <row r="72" spans="1:7" ht="84" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="8" t="s">
+      <c r="F72" s="17" t="s">
         <v>193</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>194</v>
       </c>
       <c r="G72" s="19"/>
     </row>
     <row r="73" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E73" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="G73" s="19" t="s">
         <v>196</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E74" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F74" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="G74" s="19" t="s">
         <v>199</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E75" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F75" s="17" t="s">
         <v>201</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>202</v>
       </c>
       <c r="G75" s="19"/>
     </row>
     <row r="76" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E76" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76" s="17" t="s">
         <v>203</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>204</v>
       </c>
       <c r="G76" s="19"/>
     </row>
     <row r="77" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E77" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F77" s="17" t="s">
         <v>205</v>
-      </c>
-      <c r="F77" s="17" t="s">
-        <v>206</v>
       </c>
       <c r="G77" s="19"/>
     </row>
     <row r="78" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E78" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F78" s="17" t="s">
         <v>207</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>208</v>
       </c>
       <c r="G78" s="19"/>
     </row>
     <row r="79" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E79" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F79" s="17" t="s">
         <v>209</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>210</v>
       </c>
       <c r="G79" s="19"/>
     </row>
     <row r="80" spans="1:7" ht="218.4" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E80" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F80" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="G80" s="19" t="s">
         <v>212</v>
-      </c>
-      <c r="G80" s="19" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E81" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F81" s="17" t="s">
         <v>214</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>215</v>
       </c>
       <c r="G81" s="19"/>
     </row>
     <row r="82" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E82" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="F82" s="17" t="s">
         <v>216</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>217</v>
       </c>
       <c r="G82" s="19"/>
     </row>
     <row r="83" spans="1:7" ht="84" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E83" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F83" s="17" t="s">
         <v>218</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>219</v>
       </c>
       <c r="G83" s="19"/>
     </row>
     <row r="84" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E84" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F84" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="G84" s="19" t="s">
         <v>221</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="168" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E85" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F85" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="G85" s="19" t="s">
         <v>224</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E86" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F86" s="17" t="s">
         <v>226</v>
-      </c>
-      <c r="F86" s="17" t="s">
-        <v>227</v>
       </c>
       <c r="G86" s="19"/>
     </row>
     <row r="87" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E87" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F87" s="17" t="s">
         <v>228</v>
-      </c>
-      <c r="F87" s="17" t="s">
-        <v>229</v>
       </c>
       <c r="G87" s="19"/>
     </row>
     <row r="88" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E88" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F88" s="17" t="s">
         <v>230</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>231</v>
       </c>
       <c r="G88" s="19"/>
     </row>
     <row r="89" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E89" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="F89" s="17" t="s">
         <v>232</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>233</v>
       </c>
       <c r="G89" s="19"/>
     </row>
@@ -3604,185 +3604,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB28C2F-B00A-4CCC-ABA7-07FCF92C7AC0}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="70.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="60.6640625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.88671875" style="1"/>
+    <col min="1" max="1" width="10.88671875" style="1"/>
+    <col min="2" max="2" width="14.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="70.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+      <c r="G3" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="G4" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="14" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" s="14" customFormat="1" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="G5" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8" ht="134.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
+++ b/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DC0D05-D2A6-4E58-B2A6-D5AAFAE59143}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1860E0B9-1165-4848-8577-461AF5F3DD75}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7CA062FE-945D-4C76-A68F-9B28474BFFEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA062FE-945D-4C76-A68F-9B28474BFFEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja2!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3597,7 +3598,6 @@
       <c r="F90" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G89" xr:uid="{2F067B59-0BF8-4623-BAE4-4069C82EA656}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3813,6 +3813,7 @@
       <c r="H9" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G9" xr:uid="{5AB28C2F-B00A-4CCC-ABA7-07FCF92C7AC0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
+++ b/data/CONSOLIDADO HALLAZGOS AUDITORÍA 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Dashboard-Auditoria/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1860E0B9-1165-4848-8577-461AF5F3DD75}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{CD809980-21A7-4B74-A6A8-808C59C0FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F558094-7B5E-4B6C-8E30-7BFF2AE8257A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CA062FE-945D-4C76-A68F-9B28474BFFEC}"/>
   </bookViews>
@@ -1632,6 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F067B59-0BF8-4623-BAE4-4069C82EA656}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1668,7 +1669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="13" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="13" customFormat="1" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>234</v>
       </c>
@@ -1689,7 +1690,7 @@
       </c>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>234</v>
       </c>
@@ -1710,7 +1711,7 @@
       </c>
       <c r="G3" s="12"/>
     </row>
-    <row r="4" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>234</v>
       </c>
@@ -1731,7 +1732,7 @@
       </c>
       <c r="G4" s="12"/>
     </row>
-    <row r="5" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>234</v>
       </c>
@@ -1752,7 +1753,7 @@
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>234</v>
       </c>
@@ -1775,7 +1776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>234</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>234</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
@@ -1865,7 +1866,7 @@
       </c>
       <c r="G10" s="6"/>
     </row>
-    <row r="11" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>234</v>
       </c>
@@ -1886,7 +1887,7 @@
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>234</v>
       </c>
@@ -1907,7 +1908,7 @@
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>234</v>
       </c>
@@ -1928,7 +1929,7 @@
       </c>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>234</v>
       </c>
@@ -1949,7 +1950,7 @@
       </c>
       <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>234</v>
       </c>
@@ -1970,7 +1971,7 @@
       </c>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>234</v>
       </c>
@@ -1991,7 +1992,7 @@
       </c>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>234</v>
       </c>
@@ -2014,7 +2015,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>234</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>234</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>234</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>234</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>234</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>234</v>
       </c>
@@ -2152,7 +2153,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>234</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>234</v>
       </c>
@@ -2196,7 +2197,7 @@
       </c>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>234</v>
       </c>
@@ -2217,7 +2218,7 @@
       </c>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>234</v>
       </c>
@@ -2238,7 +2239,7 @@
       </c>
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>234</v>
       </c>
@@ -2259,7 +2260,7 @@
       </c>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>234</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>234</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>234</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>234</v>
       </c>
@@ -2351,7 +2352,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>234</v>
       </c>
@@ -2374,7 +2375,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>234</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>234</v>
       </c>
@@ -2420,7 +2421,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>234</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>234</v>
       </c>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="G38" s="18"/>
     </row>
-    <row r="39" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>234</v>
       </c>
@@ -2508,7 +2509,7 @@
       </c>
       <c r="G39" s="18"/>
     </row>
-    <row r="40" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>234</v>
       </c>
@@ -2529,7 +2530,7 @@
       </c>
       <c r="G40" s="18"/>
     </row>
-    <row r="41" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>234</v>
       </c>
@@ -2550,7 +2551,7 @@
       </c>
       <c r="G41" s="18"/>
     </row>
-    <row r="42" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>234</v>
       </c>
@@ -2571,7 +2572,7 @@
       </c>
       <c r="G42" s="18"/>
     </row>
-    <row r="43" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>234</v>
       </c>
@@ -2592,7 +2593,7 @@
       </c>
       <c r="G43" s="18"/>
     </row>
-    <row r="44" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>234</v>
       </c>
@@ -2615,7 +2616,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>234</v>
       </c>
@@ -2638,7 +2639,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>234</v>
       </c>
@@ -2661,7 +2662,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>234</v>
       </c>
@@ -2684,7 +2685,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>234</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="134.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>234</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>234</v>
       </c>
@@ -2751,7 +2752,7 @@
       </c>
       <c r="G50" s="18"/>
     </row>
-    <row r="51" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>234</v>
       </c>
@@ -2772,7 +2773,7 @@
       </c>
       <c r="G51" s="18"/>
     </row>
-    <row r="52" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>234</v>
       </c>
@@ -2793,7 +2794,7 @@
       </c>
       <c r="G52" s="18"/>
     </row>
-    <row r="53" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>234</v>
       </c>
@@ -2814,7 +2815,7 @@
       </c>
       <c r="G53" s="18"/>
     </row>
-    <row r="54" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>234</v>
       </c>
@@ -2835,7 +2836,7 @@
       </c>
       <c r="G54" s="18"/>
     </row>
-    <row r="55" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>234</v>
       </c>
@@ -2858,7 +2859,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>234</v>
       </c>
@@ -2881,7 +2882,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>234</v>
       </c>
@@ -2904,7 +2905,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>234</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>234</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="134.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>234</v>
       </c>
@@ -2973,7 +2974,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="134.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>234</v>
       </c>
@@ -2996,7 +2997,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>234</v>
       </c>
@@ -3017,7 +3018,7 @@
       </c>
       <c r="G62" s="19"/>
     </row>
-    <row r="63" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>234</v>
       </c>
@@ -3038,7 +3039,7 @@
       </c>
       <c r="G63" s="19"/>
     </row>
-    <row r="64" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>234</v>
       </c>
@@ -3059,7 +3060,7 @@
       </c>
       <c r="G64" s="19"/>
     </row>
-    <row r="65" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>234</v>
       </c>
@@ -3080,7 +3081,7 @@
       </c>
       <c r="G65" s="19"/>
     </row>
-    <row r="66" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>234</v>
       </c>
@@ -3101,7 +3102,7 @@
       </c>
       <c r="G66" s="19"/>
     </row>
-    <row r="67" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>234</v>
       </c>
@@ -3122,7 +3123,7 @@
       </c>
       <c r="G67" s="19"/>
     </row>
-    <row r="68" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>234</v>
       </c>
@@ -3143,7 +3144,7 @@
       </c>
       <c r="G68" s="19"/>
     </row>
-    <row r="69" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>234</v>
       </c>
@@ -3164,7 +3165,7 @@
       </c>
       <c r="G69" s="19"/>
     </row>
-    <row r="70" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>234</v>
       </c>
@@ -3185,7 +3186,7 @@
       </c>
       <c r="G70" s="19"/>
     </row>
-    <row r="71" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>234</v>
       </c>
@@ -3206,7 +3207,7 @@
       </c>
       <c r="G71" s="19"/>
     </row>
-    <row r="72" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="67.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>234</v>
       </c>
@@ -3227,7 +3228,7 @@
       </c>
       <c r="G72" s="19"/>
     </row>
-    <row r="73" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>234</v>
       </c>
@@ -3250,7 +3251,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>234</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>234</v>
       </c>
@@ -3294,7 +3295,7 @@
       </c>
       <c r="G75" s="19"/>
     </row>
-    <row r="76" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>234</v>
       </c>
@@ -3315,7 +3316,7 @@
       </c>
       <c r="G76" s="19"/>
     </row>
-    <row r="77" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>234</v>
       </c>
@@ -3336,7 +3337,7 @@
       </c>
       <c r="G77" s="19"/>
     </row>
-    <row r="78" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>234</v>
       </c>
@@ -3357,7 +3358,7 @@
       </c>
       <c r="G78" s="19"/>
     </row>
-    <row r="79" spans="1:7" ht="117.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="117.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>234</v>
       </c>
@@ -3378,7 +3379,7 @@
       </c>
       <c r="G79" s="19"/>
     </row>
-    <row r="80" spans="1:7" ht="218.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="218.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>234</v>
       </c>
@@ -3401,7 +3402,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>234</v>
       </c>
@@ -3422,7 +3423,7 @@
       </c>
       <c r="G81" s="19"/>
     </row>
-    <row r="82" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>234</v>
       </c>
@@ -3443,7 +3444,7 @@
       </c>
       <c r="G82" s="19"/>
     </row>
-    <row r="83" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="84" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>234</v>
       </c>
@@ -3464,7 +3465,7 @@
       </c>
       <c r="G83" s="19"/>
     </row>
-    <row r="84" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>234</v>
       </c>
@@ -3487,7 +3488,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="168" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="168" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>234</v>
       </c>
@@ -3510,7 +3511,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>234</v>
       </c>
@@ -3531,7 +3532,7 @@
       </c>
       <c r="G86" s="19"/>
     </row>
-    <row r="87" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>234</v>
       </c>
@@ -3552,7 +3553,7 @@
       </c>
       <c r="G87" s="19"/>
     </row>
-    <row r="88" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="184.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>234</v>
       </c>
@@ -3573,7 +3574,7 @@
       </c>
       <c r="G88" s="19"/>
     </row>
-    <row r="89" spans="1:7" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="134.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>234</v>
       </c>
@@ -3598,6 +3599,13 @@
       <c r="F90" s="20"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G89" xr:uid="{2F067B59-0BF8-4623-BAE4-4069C82EA656}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Nuevo Riesgo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
